--- a/outputs/56920.xlsx
+++ b/outputs/56920.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t xml:space="preserve">Description</t>
   </si>
@@ -31,10 +31,19 @@
     <t xml:space="preserve">2020-01-20/AF/TES-9558383838 ZYP0-Critical Instructions</t>
   </si>
   <si>
+    <t xml:space="preserve">9558383838</t>
+  </si>
+  <si>
     <t xml:space="preserve">2020-02-02/AF20/TES-9558384028 ZYP0-Normal Query</t>
   </si>
   <si>
+    <t xml:space="preserve">9558384028</t>
+  </si>
+  <si>
     <t xml:space="preserve">2021-01-20/BST2090/TES-9558385555 ZYP0-Fiber Quotas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9558385555</t>
   </si>
   <si>
     <t xml:space="preserve">2021-01-20/BST2090/AQX-CHK8385343 ZYPX-Olive Box</t>
@@ -129,16 +138,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -334,70 +347,55 @@
   <dimension ref="B2:C8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="57.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="57.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="0" t="str">
-        <f aca="false">IF(ISNUMBER(SEARCH("955",B3)),MID(B3,SEARCH("955",B3),10),IF(ISNUMBER(SEARCH("CHK",B3)),MID(B3,SEARCH("CHK",B3),10),""))</f>
-        <v>9558383838</v>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="0" t="str">
-        <f aca="false">IF(ISNUMBER(SEARCH("955",B4)),MID(B4,SEARCH("955",B4),10),IF(ISNUMBER(SEARCH("CHK",B4)),MID(B4,SEARCH("CHK",B4),10),""))</f>
-        <v>9558384028</v>
+      <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="0" t="str">
-        <f aca="false">IF(ISNUMBER(SEARCH("955",B5)),MID(B5,SEARCH("955",B5),10),IF(ISNUMBER(SEARCH("CHK",B5)),MID(B5,SEARCH("CHK",B5),10),""))</f>
-        <v>9558385555</v>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="0" t="str">
-        <f aca="false">IF(ISNUMBER(SEARCH("955",B6)),MID(B6,SEARCH("955",B6),10),IF(ISNUMBER(SEARCH("CHK",B6)),MID(B6,SEARCH("CHK",B6),10),""))</f>
-        <v>9558385555</v>
+      <c r="B6" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="0" t="str">
-        <f aca="false">IF(ISNUMBER(SEARCH("955",B7)),MID(B7,SEARCH("955",B7),10),IF(ISNUMBER(SEARCH("CHK",B7)),MID(B7,SEARCH("CHK",B7),10),""))</f>
-        <v>CHK8385343</v>
+      <c r="B7" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="0" t="str">
-        <f aca="false">IF(ISNUMBER(SEARCH("955",B8)),MID(B8,SEARCH("955",B8),10),IF(ISNUMBER(SEARCH("CHK",B8)),MID(B8,SEARCH("CHK",B8),10),""))</f>
-        <v>CHK8395240</v>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/56920.xlsx
+++ b/outputs/56920.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
   <si>
     <t xml:space="preserve">Description</t>
   </si>
@@ -31,19 +31,10 @@
     <t xml:space="preserve">2020-01-20/AF/TES-9558383838 ZYP0-Critical Instructions</t>
   </si>
   <si>
-    <t xml:space="preserve">9558383838</t>
-  </si>
-  <si>
     <t xml:space="preserve">2020-02-02/AF20/TES-9558384028 ZYP0-Normal Query</t>
   </si>
   <si>
-    <t xml:space="preserve">9558384028</t>
-  </si>
-  <si>
     <t xml:space="preserve">2021-01-20/BST2090/TES-9558385555 ZYP0-Fiber Quotas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9558385555</t>
   </si>
   <si>
     <t xml:space="preserve">2021-01-20/BST2090/AQX-CHK8385343 ZYPX-Olive Box</t>
@@ -363,39 +354,54 @@
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
+      <c r="C3" s="1" t="str">
+        <f aca="false">IFERROR(MID(B3,FIND("955",B3),10),IFERROR(MID(B3,FIND("CHK",B3),10),""))</f>
+        <v>9558383838</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="str">
+        <f aca="false">IFERROR(MID(B4,FIND("955",B4),10),IFERROR(MID(B4,FIND("CHK",B4),10),""))</f>
+        <v>9558384028</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="C5" s="1" t="str">
+        <f aca="false">IFERROR(MID(B5,FIND("955",B5),10),IFERROR(MID(B5,FIND("CHK",B5),10),""))</f>
+        <v>9558385555</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="str">
+        <f aca="false">IFERROR(MID(B6,FIND("955",B6),10),IFERROR(MID(B6,FIND("CHK",B6),10),""))</f>
+        <v>9558385555</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="3" t="s">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="C7" s="1" t="str">
+        <f aca="false">IFERROR(MID(B7,FIND("955",B7),10),IFERROR(MID(B7,FIND("CHK",B7),10),""))</f>
+        <v>CHK8385343</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
+      </c>
+      <c r="C8" s="1" t="str">
+        <f aca="false">IFERROR(MID(B8,FIND("955",B8),10),IFERROR(MID(B8,FIND("CHK",B8),10),""))</f>
+        <v>CHK8395240</v>
       </c>
     </row>
   </sheetData>
